--- a/Clase/US_Clase.xlsx
+++ b/Clase/US_Clase.xlsx
@@ -680,13 +680,13 @@
         <v>1.900708318697975</v>
       </c>
       <c r="C2" s="2">
-        <v>107.6298833645245</v>
+        <v>108.0411988152773</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>2.045730146514446</v>
+        <v>2.053548053502993</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -711,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>4.558501495702155</v>
+        <v>4.558501495702154</v>
       </c>
       <c r="C4" s="2">
         <v>119.7209036206214</v>
@@ -1230,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="2">
-        <v>4.884418886761806</v>
+        <v>4.884418886761807</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1417,7 +1417,7 @@
         <v>6</v>
       </c>
       <c r="E45" s="2">
-        <v>0.8464465441640308</v>
+        <v>0.8464465441640304</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1527,7 +1527,7 @@
         <v>56</v>
       </c>
       <c r="B52" s="2">
-        <v>0.4721041503685125</v>
+        <v>0.4721041503685126</v>
       </c>
       <c r="C52" s="2">
         <v>105.2751089775506</v>
@@ -1536,7 +1536,7 @@
         <v>6</v>
       </c>
       <c r="E52" s="2">
-        <v>0.4970081587879908</v>
+        <v>0.4970081587879909</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1544,7 +1544,7 @@
         <v>57</v>
       </c>
       <c r="B53" s="2">
-        <v>1.70826067340528</v>
+        <v>1.708260673405281</v>
       </c>
       <c r="C53" s="2">
         <v>104.6386860394234</v>
@@ -1553,7 +1553,7 @@
         <v>6</v>
       </c>
       <c r="E53" s="2">
-        <v>1.787501522779491</v>
+        <v>1.787501522779492</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1689,7 +1689,7 @@
         <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>3.548140672330238</v>
+        <v>3.548140672330237</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1969,7 +1969,7 @@
         <v>82</v>
       </c>
       <c r="B78" s="2">
-        <v>15.2954289353786</v>
+        <v>15.29542893537859</v>
       </c>
       <c r="C78" s="2">
         <v>117.673969373352</v>
